--- a/docs/asset-management/PromptCraft_Visual_Asset_Tracker_Simplified.xlsx
+++ b/docs/asset-management/PromptCraft_Visual_Asset_Tracker_Simplified.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 Artwork" sheetId="1" r:id="R795e60d4cf5e455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Artwork" sheetId="2" r:id="R19939427b34448ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy S1" sheetId="3" r:id="R8146d6f954634650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1 Artwork" sheetId="1" r:id="R1535f333cd114497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Artwork" sheetId="2" r:id="R55bfaf2edfc142e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy S1" sheetId="3" r:id="R31f38cb058c342d1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -341,11 +341,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Scenario 1 artwork</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>All current art exists. Check framing before requesting replacements.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -369,7 +387,7 @@
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>app-background.png</x:v>
+        <x:v>bg_01_app.png</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>Background</x:v>
@@ -384,12 +402,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>assets/images/backgrounds/app-background.png</x:v>
+        <x:v>assets/images/backgrounds/bg_01_app.png</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>classroom.png</x:v>
+        <x:v>bg_02_classroom.png</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>Background</x:v>
@@ -404,12 +422,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
-        <x:v>assets/images/backgrounds/classroom.png</x:v>
+        <x:v>assets/images/backgrounds/bg_02_classroom.png</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>s1-science-wing.jpg</x:v>
+        <x:v>bg_s01_01_science_wing.jpg</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>Background</x:v>
@@ -424,12 +442,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>assets/images/backgrounds/gfc/s1-science-wing.jpg</x:v>
+        <x:v>assets/images/backgrounds/gfc/bg_s01_01_science_wing.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>encouraging.png</x:v>
+        <x:v>pp_04_encouraging.png</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -444,12 +462,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/encouraging.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_04_encouraging.png</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>excited.png</x:v>
+        <x:v>pp_03_excited.png</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -464,12 +482,12 @@
         <x:v>No new art needed</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/excited.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_03_excited.png</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>pp_01_neutral.png</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -484,12 +502,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/neutral.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_01_neutral.png</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>proud.png</x:v>
+        <x:v>pp_06_proud.png</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -504,12 +522,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/proud.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_06_proud.png</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>skeptical.png</x:v>
+        <x:v>pp_05_skeptical.png</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -524,12 +542,12 @@
         <x:v>No new art needed</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/skeptical.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_05_skeptical.png</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>pp_02_thinking.png</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -544,12 +562,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/thinking.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_02_thinking.png</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>confident.png</x:v>
+        <x:v>maya_05_confident.png</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -564,12 +582,12 @@
         <x:v>No new art needed</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/confident.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_05_confident.png</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>frustrated.png</x:v>
+        <x:v>maya_04_frustrated.png</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -584,12 +602,12 @@
         <x:v>No new art needed</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/frustrated.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_04_frustrated.png</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>maya_01_neutral.png</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -604,12 +622,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/neutral.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_01_neutral.png</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>maya_02_thinking.png</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -624,12 +642,12 @@
         <x:v>No new art needed</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/thinking.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_02_thinking.png</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>uncertain.png</x:v>
+        <x:v>maya_03_uncertain.png</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -644,12 +662,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/uncertain.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_03_uncertain.png</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>babbage-engine.webp</x:v>
+        <x:v>ui_02_babbage_engine.webp</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -664,12 +682,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>assets/images/ui/babbage-engine.webp</x:v>
+        <x:v>assets/images/ui/ui_02_babbage_engine.webp</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>babbage-mark.svg</x:v>
+        <x:v>ui_01_babbage_mark.svg</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -684,12 +702,12 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>assets/images/ui/babbage-mark.svg</x:v>
+        <x:v>assets/images/ui/ui_01_babbage_mark.svg</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>mo-river-otter.png</x:v>
+        <x:v>ui_04_mo_river_otter.png</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -704,7 +722,7 @@
         <x:v>Check framing</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>assets/images/ui/mo-river-otter.png</x:v>
+        <x:v>assets/images/ui/ui_04_mo_river_otter.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -715,7 +733,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bc2a1c7d135466e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dc1b53618314d11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -736,11 +754,29 @@
       <x:c r="A2" s="1" t="str">
         <x:v>All artwork files</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
+      <x:c r="F2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
-        <x:v>Full asset inventory from the filesystem and manifest v150.</x:v>
-      </x:c>
+        <x:v>Full asset inventory from the filesystem and manifest v151.</x:v>
+      </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+      <x:c r="F3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
+      <x:c r="F4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -764,7 +800,7 @@
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>app-background.png</x:v>
+        <x:v>bg_01_app.png</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>Background</x:v>
@@ -776,15 +812,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
-        <x:v>assets/images/backgrounds/app-background.png</x:v>
+        <x:v>assets/images/backgrounds/bg_01_app.png</x:v>
       </x:c>
       <x:c r="F6" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>classroom.png</x:v>
+        <x:v>bg_02_classroom.png</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>Background</x:v>
@@ -796,15 +832,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
-        <x:v>assets/images/backgrounds/classroom.png</x:v>
+        <x:v>assets/images/backgrounds/bg_02_classroom.png</x:v>
       </x:c>
       <x:c r="F7" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>desk-extension.png</x:v>
+        <x:v>bg_03_desk_extension.png</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>Background</x:v>
@@ -816,15 +852,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>assets/images/backgrounds/desk-extension.png</x:v>
+        <x:v>assets/images/backgrounds/bg_03_desk_extension.png</x:v>
       </x:c>
       <x:c r="F8" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>s1-science-wing.jpg</x:v>
+        <x:v>bg_s01_01_science_wing.jpg</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
         <x:v>Background</x:v>
@@ -836,15 +872,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>assets/images/backgrounds/gfc/s1-science-wing.jpg</x:v>
+        <x:v>assets/images/backgrounds/gfc/bg_s01_01_science_wing.jpg</x:v>
       </x:c>
       <x:c r="F9" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>s2-study-lounge.jpg</x:v>
+        <x:v>bg_s02_01_study_lounge.jpg</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
         <x:v>Background</x:v>
@@ -856,15 +892,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>assets/images/backgrounds/gfc/s2-study-lounge.jpg</x:v>
+        <x:v>assets/images/backgrounds/gfc/bg_s02_01_study_lounge.jpg</x:v>
       </x:c>
       <x:c r="F10" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>encouraging.png</x:v>
+        <x:v>pp_04_encouraging.png</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -876,15 +912,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/encouraging.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_04_encouraging.png</x:v>
       </x:c>
       <x:c r="F11" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>excited.png</x:v>
+        <x:v>pp_03_excited.png</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -896,15 +932,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/excited.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_03_excited.png</x:v>
       </x:c>
       <x:c r="F12" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>pp_01_neutral.png</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -916,15 +952,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/neutral.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_01_neutral.png</x:v>
       </x:c>
       <x:c r="F13" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>proud.png</x:v>
+        <x:v>pp_06_proud.png</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -936,15 +972,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/proud.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_06_proud.png</x:v>
       </x:c>
       <x:c r="F14" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>skeptical.png</x:v>
+        <x:v>pp_05_skeptical.png</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -956,15 +992,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/skeptical.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_05_skeptical.png</x:v>
       </x:c>
       <x:c r="F15" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>pp_02_thinking.png</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
         <x:v>Character - Professor Pixel</x:v>
@@ -976,15 +1012,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>assets/images/characters/professor-pixel/thinking.png</x:v>
+        <x:v>assets/images/characters/professor-pixel/pp_02_thinking.png</x:v>
       </x:c>
       <x:c r="F16" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>concept-sheet.png</x:v>
+        <x:v>devon_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -996,15 +1032,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>assets/images/characters/students/devon/references/concept-sheet.png</x:v>
+        <x:v>assets/images/characters/students/devon/references/devon_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="F17" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>confident.png</x:v>
+        <x:v>eli_05_confident.png</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1016,15 +1052,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/confident.png</x:v>
+        <x:v>assets/images/characters/students/eli/eli_05_confident.png</x:v>
       </x:c>
       <x:c r="F18" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>frustrated.png</x:v>
+        <x:v>eli_04_frustrated.png</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1036,15 +1072,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/frustrated.png</x:v>
+        <x:v>assets/images/characters/students/eli/eli_04_frustrated.png</x:v>
       </x:c>
       <x:c r="F19" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>eli_01_neutral.png</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1056,15 +1092,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/neutral.png</x:v>
+        <x:v>assets/images/characters/students/eli/eli_01_neutral.png</x:v>
       </x:c>
       <x:c r="F20" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>concept-sheet.png</x:v>
+        <x:v>eli_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1076,15 +1112,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/references/concept-sheet.png</x:v>
+        <x:v>assets/images/characters/students/eli/references/eli_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="F21" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>eli_02_thinking.png</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1096,15 +1132,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/thinking.png</x:v>
+        <x:v>assets/images/characters/students/eli/eli_02_thinking.png</x:v>
       </x:c>
       <x:c r="F22" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>uncertain.png</x:v>
+        <x:v>eli_03_uncertain.png</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1116,15 +1152,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>assets/images/characters/students/eli/uncertain.png</x:v>
+        <x:v>assets/images/characters/students/eli/eli_03_uncertain.png</x:v>
       </x:c>
       <x:c r="F23" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>confident.png</x:v>
+        <x:v>jordan_05_confident.png</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1136,15 +1172,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/confident.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_05_confident.png</x:v>
       </x:c>
       <x:c r="F24" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>dryly-amused.png</x:v>
+        <x:v>jordan_06_dryly_amused.png</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1156,15 +1192,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/dryly-amused.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_06_dryly_amused.png</x:v>
       </x:c>
       <x:c r="F25" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>frustrated.png</x:v>
+        <x:v>jordan_04_frustrated.png</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1176,15 +1212,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/frustrated.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_04_frustrated.png</x:v>
       </x:c>
       <x:c r="F26" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>jordan_01_neutral.png</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1196,15 +1232,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/neutral.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_01_neutral.png</x:v>
       </x:c>
       <x:c r="F27" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>jordan_02_thinking.png</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1216,15 +1252,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/thinking.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_02_thinking.png</x:v>
       </x:c>
       <x:c r="F28" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>uncertain.png</x:v>
+        <x:v>jordan_03_uncertain.png</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1236,15 +1272,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
-        <x:v>assets/images/characters/students/jordan/uncertain.png</x:v>
+        <x:v>assets/images/characters/students/jordan/jordan_03_uncertain.png</x:v>
       </x:c>
       <x:c r="F29" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>concept-sheet.png</x:v>
+        <x:v>lena_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1256,15 +1292,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
-        <x:v>assets/images/characters/students/lena/references/concept-sheet.png</x:v>
+        <x:v>assets/images/characters/students/lena/references/lena_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="F30" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="27" customHeight="1">
       <x:c r="A31" s="7" t="str">
-        <x:v>confident.png</x:v>
+        <x:v>maya_05_confident.png</x:v>
       </x:c>
       <x:c r="B31" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1276,15 +1312,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E31" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/confident.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_05_confident.png</x:v>
       </x:c>
       <x:c r="F31" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="27" customHeight="1">
       <x:c r="A32" s="7" t="str">
-        <x:v>frustrated.png</x:v>
+        <x:v>maya_04_frustrated.png</x:v>
       </x:c>
       <x:c r="B32" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1296,15 +1332,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E32" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/frustrated.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_04_frustrated.png</x:v>
       </x:c>
       <x:c r="F32" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="27" customHeight="1">
       <x:c r="A33" s="7" t="str">
-        <x:v>neutral.png</x:v>
+        <x:v>maya_01_neutral.png</x:v>
       </x:c>
       <x:c r="B33" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1316,15 +1352,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E33" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/neutral.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_01_neutral.png</x:v>
       </x:c>
       <x:c r="F33" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="27" customHeight="1">
       <x:c r="A34" s="7" t="str">
-        <x:v>thinking.png</x:v>
+        <x:v>maya_02_thinking.png</x:v>
       </x:c>
       <x:c r="B34" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1336,15 +1372,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E34" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/thinking.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_02_thinking.png</x:v>
       </x:c>
       <x:c r="F34" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="27" customHeight="1">
       <x:c r="A35" s="7" t="str">
-        <x:v>uncertain.png</x:v>
+        <x:v>maya_03_uncertain.png</x:v>
       </x:c>
       <x:c r="B35" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1356,15 +1392,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E35" s="7" t="str">
-        <x:v>assets/images/characters/students/maya/uncertain.png</x:v>
+        <x:v>assets/images/characters/students/maya/maya_03_uncertain.png</x:v>
       </x:c>
       <x:c r="F35" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="27" customHeight="1">
       <x:c r="A36" s="7" t="str">
-        <x:v>concept-sheet.png</x:v>
+        <x:v>samira_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="B36" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1376,15 +1412,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E36" s="7" t="str">
-        <x:v>assets/images/characters/students/samira/references/concept-sheet.png</x:v>
+        <x:v>assets/images/characters/students/samira/references/samira_ref_01_concept_sheet.png</x:v>
       </x:c>
       <x:c r="F36" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="27" customHeight="1">
       <x:c r="A37" s="7" t="str">
-        <x:v>student-cast-concept-sheet.png</x:v>
+        <x:v>ref_01_student_cast.png</x:v>
       </x:c>
       <x:c r="B37" s="7" t="str">
         <x:v>Character - Student</x:v>
@@ -1396,15 +1432,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E37" s="7" t="str">
-        <x:v>assets/images/characters/students/student-cast-concept-sheet.png</x:v>
+        <x:v>assets/images/characters/students/ref_01_student_cast.png</x:v>
       </x:c>
       <x:c r="F37" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="27" customHeight="1">
       <x:c r="A38" s="7" t="str">
-        <x:v>all-scenarios-complete.png</x:v>
+        <x:v>end_01_all_scenarios.png</x:v>
       </x:c>
       <x:c r="B38" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -1416,15 +1452,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E38" s="7" t="str">
-        <x:v>assets/images/scenes/completion/all-scenarios-complete.png</x:v>
+        <x:v>assets/images/scenes/completion/end_01_all_scenarios.png</x:v>
       </x:c>
       <x:c r="F38" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="27" customHeight="1">
       <x:c r="A39" s="7" t="str">
-        <x:v>instructor-after-module.png</x:v>
+        <x:v>legacy_s01_canvas_04_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="B39" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1436,15 +1472,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E39" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_04_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="F39" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="27" customHeight="1">
       <x:c r="A40" s="7" t="str">
-        <x:v>instructor-after-read-page.png</x:v>
+        <x:v>legacy_s01_canvas_10_instructor_after_read.png</x:v>
       </x:c>
       <x:c r="B40" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1456,15 +1492,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E40" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-read-page.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_10_instructor_after_read.png</x:v>
       </x:c>
       <x:c r="F40" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="27" customHeight="1">
       <x:c r="A41" s="7" t="str">
-        <x:v>instructor-after-start-here.png</x:v>
+        <x:v>legacy_s01_canvas_08_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="B41" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1476,15 +1512,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E41" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-start-here.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_08_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="F41" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="27" customHeight="1">
       <x:c r="A42" s="7" t="str">
-        <x:v>instructor-after-submit-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_09_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="B42" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1496,15 +1532,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E42" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-submit-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_09_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="F42" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="27" customHeight="1">
       <x:c r="A43" s="7" t="str">
-        <x:v>instructor-before-buried-directions.png</x:v>
+        <x:v>legacy_s01_canvas_07_instructor_before_buried_directions.png</x:v>
       </x:c>
       <x:c r="B43" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1516,15 +1552,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E43" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-buried-directions.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_07_instructor_before_buried_directions.png</x:v>
       </x:c>
       <x:c r="F43" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="27" customHeight="1">
       <x:c r="A44" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_06_instructor_before_comparison.png</x:v>
       </x:c>
       <x:c r="B44" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1536,15 +1572,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E44" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-comparison-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_06_instructor_before_comparison.png</x:v>
       </x:c>
       <x:c r="F44" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="27" customHeight="1">
       <x:c r="A45" s="7" t="str">
-        <x:v>instructor-before-module-mobile-phone.png</x:v>
+        <x:v>legacy_s01_canvas_03_instructor_before_module_phone.png</x:v>
       </x:c>
       <x:c r="B45" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1556,15 +1592,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E45" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module-mobile-phone.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_03_instructor_before_module_phone.png</x:v>
       </x:c>
       <x:c r="F45" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="27" customHeight="1">
       <x:c r="A46" s="7" t="str">
-        <x:v>instructor-before-module-mobile-wide.png</x:v>
+        <x:v>legacy_s01_canvas_02_instructor_before_module_wide.png</x:v>
       </x:c>
       <x:c r="B46" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1576,15 +1612,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E46" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module-mobile-wide.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_02_instructor_before_module_wide.png</x:v>
       </x:c>
       <x:c r="F46" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="27" customHeight="1">
       <x:c r="A47" s="7" t="str">
-        <x:v>instructor-before-module.png</x:v>
+        <x:v>legacy_s01_canvas_01_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="B47" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1596,15 +1632,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E47" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_01_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="F47" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="27" customHeight="1">
       <x:c r="A48" s="7" t="str">
-        <x:v>instructor-before-week-4-notes.png</x:v>
+        <x:v>legacy_s01_canvas_05_instructor_before_week4_notes.png</x:v>
       </x:c>
       <x:c r="B48" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1616,15 +1652,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E48" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-week-4-notes.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_05_instructor_before_week4_notes.png</x:v>
       </x:c>
       <x:c r="F48" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="27" customHeight="1">
       <x:c r="A49" s="7" t="str">
-        <x:v>instructor-after-module-focus.png</x:v>
+        <x:v>legacy_s01_board_18_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="B49" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1636,15 +1672,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E49" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_18_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="F49" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="27" customHeight="1">
       <x:c r="A50" s="7" t="str">
-        <x:v>instructor-after-start-here-focus.png</x:v>
+        <x:v>legacy_s01_board_24_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="B50" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1656,15 +1692,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E50" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-start-here-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_24_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="F50" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="27" customHeight="1">
       <x:c r="A51" s="7" t="str">
-        <x:v>instructor-after-submit-assignment-focus.png</x:v>
+        <x:v>legacy_s01_board_22_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="B51" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1676,15 +1712,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E51" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-submit-assignment-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_22_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="F51" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="27" customHeight="1">
       <x:c r="A52" s="7" t="str">
-        <x:v>instructor-before-buried-directions-focus.png</x:v>
+        <x:v>legacy_s01_board_23_instructor_before_buried.png</x:v>
       </x:c>
       <x:c r="B52" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1696,15 +1732,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E52" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-buried-directions-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_23_instructor_before_buried.png</x:v>
       </x:c>
       <x:c r="F52" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="27" customHeight="1">
       <x:c r="A53" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment-focus.png</x:v>
+        <x:v>legacy_s01_board_25_instructor_before_comparison_reference.png</x:v>
       </x:c>
       <x:c r="B53" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1716,15 +1752,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E53" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-comparison-assignment-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_25_instructor_before_comparison_reference.png</x:v>
       </x:c>
       <x:c r="F53" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="27" customHeight="1">
       <x:c r="A54" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment-safe-focus.png</x:v>
+        <x:v>legacy_s01_board_21_instructor_before_comparison_safe.png</x:v>
       </x:c>
       <x:c r="B54" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1736,15 +1772,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E54" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-comparison-assignment-safe-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_21_instructor_before_comparison_safe.png</x:v>
       </x:c>
       <x:c r="F54" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27" customHeight="1">
       <x:c r="A55" s="7" t="str">
-        <x:v>instructor-before-module-focus.png</x:v>
+        <x:v>legacy_s01_board_17_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="B55" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1756,15 +1792,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E55" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_17_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="F55" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="27" customHeight="1">
       <x:c r="A56" s="7" t="str">
-        <x:v>student-after-module-focus.png</x:v>
+        <x:v>legacy_s01_board_20_student_after_module.png</x:v>
       </x:c>
       <x:c r="B56" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1776,15 +1812,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E56" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/student-after-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_20_student_after_module.png</x:v>
       </x:c>
       <x:c r="F56" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="27" customHeight="1">
       <x:c r="A57" s="7" t="str">
-        <x:v>student-before-module-focus.png</x:v>
+        <x:v>legacy_s01_board_19_student_before_module.png</x:v>
       </x:c>
       <x:c r="B57" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1796,15 +1832,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E57" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/student-before-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_19_student_before_module.png</x:v>
       </x:c>
       <x:c r="F57" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="27" customHeight="1">
       <x:c r="A58" s="7" t="str">
-        <x:v>student-after-module.png</x:v>
+        <x:v>legacy_s01_canvas_14_student_after_module.png</x:v>
       </x:c>
       <x:c r="B58" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1816,15 +1852,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E58" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-after-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_14_student_after_module.png</x:v>
       </x:c>
       <x:c r="F58" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="27" customHeight="1">
       <x:c r="A59" s="7" t="str">
-        <x:v>student-after-start-here.png</x:v>
+        <x:v>legacy_s01_canvas_16_student_after_start_here.png</x:v>
       </x:c>
       <x:c r="B59" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1836,15 +1872,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E59" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-after-start-here.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_16_student_after_start_here.png</x:v>
       </x:c>
       <x:c r="F59" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="27" customHeight="1">
       <x:c r="A60" s="7" t="str">
-        <x:v>student-before-comparison-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_15_student_before_comparison.png</x:v>
       </x:c>
       <x:c r="B60" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1856,15 +1892,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E60" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-comparison-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_15_student_before_comparison.png</x:v>
       </x:c>
       <x:c r="F60" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="27" customHeight="1">
       <x:c r="A61" s="7" t="str">
-        <x:v>student-before-module-mobile-phone.png</x:v>
+        <x:v>legacy_s01_canvas_13_student_before_module_phone.png</x:v>
       </x:c>
       <x:c r="B61" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1876,15 +1912,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E61" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module-mobile-phone.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_13_student_before_module_phone.png</x:v>
       </x:c>
       <x:c r="F61" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="27" customHeight="1">
       <x:c r="A62" s="7" t="str">
-        <x:v>student-before-module-mobile-wide.png</x:v>
+        <x:v>legacy_s01_canvas_12_student_before_module_wide.png</x:v>
       </x:c>
       <x:c r="B62" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1896,15 +1932,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E62" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module-mobile-wide.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_12_student_before_module_wide.png</x:v>
       </x:c>
       <x:c r="F62" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="27" customHeight="1">
       <x:c r="A63" s="7" t="str">
-        <x:v>student-before-module.png</x:v>
+        <x:v>legacy_s01_canvas_11_student_before_module.png</x:v>
       </x:c>
       <x:c r="B63" s="7" t="str">
         <x:v>Canvas evidence</x:v>
@@ -1916,15 +1952,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E63" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_11_student_before_module.png</x:v>
       </x:c>
       <x:c r="F63" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="27" customHeight="1">
       <x:c r="A64" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s01_legacy_01_scene.png</x:v>
       </x:c>
       <x:c r="B64" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -1936,15 +1972,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E64" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-engagement/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-engagement/s01_legacy_01_scene.png</x:v>
       </x:c>
       <x:c r="F64" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="27" customHeight="1">
       <x:c r="A65" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s02_01_scene.png</x:v>
       </x:c>
       <x:c r="B65" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -1956,15 +1992,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E65" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-02-metacognition/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-02-metacognition/s02_01_scene.png</x:v>
       </x:c>
       <x:c r="F65" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="27" customHeight="1">
       <x:c r="A66" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s03_01_scene.png</x:v>
       </x:c>
       <x:c r="B66" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -1976,15 +2012,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E66" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-03-authentic-assessment/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-03-authentic-assessment/s03_01_scene.png</x:v>
       </x:c>
       <x:c r="F66" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="27" customHeight="1">
       <x:c r="A67" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s04_01_scene.png</x:v>
       </x:c>
       <x:c r="B67" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -1996,15 +2032,15 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="E67" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-04-sync-bias/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-04-sync-bias/s04_01_scene.png</x:v>
       </x:c>
       <x:c r="F67" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="27" customHeight="1">
       <x:c r="A68" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s05_01_scene.png</x:v>
       </x:c>
       <x:c r="B68" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -2016,15 +2052,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E68" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-05-hallucination-hunt/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-05-hallucination-hunt/s05_01_scene.png</x:v>
       </x:c>
       <x:c r="F68" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="27" customHeight="1">
       <x:c r="A69" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s06_01_scene.png</x:v>
       </x:c>
       <x:c r="B69" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -2036,15 +2072,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E69" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-06-predict-output/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-06-predict-output/s06_01_scene.png</x:v>
       </x:c>
       <x:c r="F69" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="27" customHeight="1">
       <x:c r="A70" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s07_01_scene.png</x:v>
       </x:c>
       <x:c r="B70" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -2056,15 +2092,15 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="E70" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-07-overreliance/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-07-overreliance/s07_01_scene.png</x:v>
       </x:c>
       <x:c r="F70" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="27" customHeight="1">
       <x:c r="A71" s="7" t="str">
-        <x:v>scene.png</x:v>
+        <x:v>s08_01_scene.png</x:v>
       </x:c>
       <x:c r="B71" s="7" t="str">
         <x:v>Scene art</x:v>
@@ -2076,15 +2112,15 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="E71" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-08-reflect-revise/scene.png</x:v>
+        <x:v>assets/images/scenes/scenario-08-reflect-revise/s08_01_scene.png</x:v>
       </x:c>
       <x:c r="F71" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="27" customHeight="1">
       <x:c r="A72" s="7" t="str">
-        <x:v>babbage-engine-plate.svg</x:v>
+        <x:v>ui_05_babbage_engine_plate.svg</x:v>
       </x:c>
       <x:c r="B72" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2096,15 +2132,15 @@
         <x:v>Reference</x:v>
       </x:c>
       <x:c r="E72" s="7" t="str">
-        <x:v>assets/images/ui/babbage-engine-plate.svg</x:v>
+        <x:v>assets/images/ui/ui_05_babbage_engine_plate.svg</x:v>
       </x:c>
       <x:c r="F72" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="27" customHeight="1">
       <x:c r="A73" s="7" t="str">
-        <x:v>babbage-engine.webp</x:v>
+        <x:v>ui_02_babbage_engine.webp</x:v>
       </x:c>
       <x:c r="B73" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2116,15 +2152,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E73" s="7" t="str">
-        <x:v>assets/images/ui/babbage-engine.webp</x:v>
+        <x:v>assets/images/ui/ui_02_babbage_engine.webp</x:v>
       </x:c>
       <x:c r="F73" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="27" customHeight="1">
       <x:c r="A74" s="7" t="str">
-        <x:v>babbage-mark.svg</x:v>
+        <x:v>ui_01_babbage_mark.svg</x:v>
       </x:c>
       <x:c r="B74" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2136,15 +2172,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E74" s="7" t="str">
-        <x:v>assets/images/ui/babbage-mark.svg</x:v>
+        <x:v>assets/images/ui/ui_01_babbage_mark.svg</x:v>
       </x:c>
       <x:c r="F74" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="27" customHeight="1">
       <x:c r="A75" s="7" t="str">
-        <x:v>charles-babbage.png</x:v>
+        <x:v>ui_03_charles_babbage.png</x:v>
       </x:c>
       <x:c r="B75" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2156,15 +2192,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E75" s="7" t="str">
-        <x:v>assets/images/ui/charles-babbage.png</x:v>
+        <x:v>assets/images/ui/ui_03_charles_babbage.png</x:v>
       </x:c>
       <x:c r="F75" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="27" customHeight="1">
       <x:c r="A76" s="7" t="str">
-        <x:v>mo-river-otter.png</x:v>
+        <x:v>ui_04_mo_river_otter.png</x:v>
       </x:c>
       <x:c r="B76" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2176,15 +2212,15 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E76" s="7" t="str">
-        <x:v>assets/images/ui/mo-river-otter.png</x:v>
+        <x:v>assets/images/ui/ui_04_mo_river_otter.png</x:v>
       </x:c>
       <x:c r="F76" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="27" customHeight="1">
       <x:c r="A77" s="7" t="str">
-        <x:v>promptcraft-qr.png</x:v>
+        <x:v>ui_06_promptcraft_qr.png</x:v>
       </x:c>
       <x:c r="B77" s="7" t="str">
         <x:v>UI and brand</x:v>
@@ -2196,16 +2232,16 @@
         <x:v>Runtime</x:v>
       </x:c>
       <x:c r="E77" s="7" t="str">
-        <x:v>assets/ui/promptcraft-qr.png</x:v>
+        <x:v>assets/ui/ui_06_promptcraft_qr.png</x:v>
       </x:c>
       <x:c r="F77" s="7" t="str">
-        <x:v>Manifest v150 classification</x:v>
+        <x:v>Manifest v151 classification</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R487aac00444643c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59200eff20664333"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2225,11 +2261,26 @@
       <x:c r="A2" s="1" t="str">
         <x:v>Older Scenario 1 artwork</x:v>
       </x:c>
+      <x:c r="B2"/>
+      <x:c r="C2"/>
+      <x:c r="D2"/>
+      <x:c r="E2"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
       <x:c r="A3" s="2" t="str">
         <x:v>These Content Avalanche captures remain registered but are not requested by the current Start With the Learning route.</x:v>
       </x:c>
+      <x:c r="B3"/>
+      <x:c r="C3"/>
+      <x:c r="D3"/>
+      <x:c r="E3"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4"/>
+      <x:c r="B4"/>
+      <x:c r="C4"/>
+      <x:c r="D4"/>
+      <x:c r="E4"/>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
       <x:c r="A5" s="5" t="str">
@@ -2250,7 +2301,7 @@
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
       <x:c r="A6" s="7" t="str">
-        <x:v>instructor-after-module.png</x:v>
+        <x:v>legacy_s01_canvas_04_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="B6" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2262,12 +2313,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E6" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_04_instructor_after_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
       <x:c r="A7" s="7" t="str">
-        <x:v>instructor-after-read-page.png</x:v>
+        <x:v>legacy_s01_canvas_10_instructor_after_read.png</x:v>
       </x:c>
       <x:c r="B7" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2279,12 +2330,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E7" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-read-page.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_10_instructor_after_read.png</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="7" t="str">
-        <x:v>instructor-after-start-here.png</x:v>
+        <x:v>legacy_s01_canvas_08_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="B8" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2296,12 +2347,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E8" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-start-here.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_08_instructor_after_start_here.png</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
       <x:c r="A9" s="7" t="str">
-        <x:v>instructor-after-submit-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_09_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="B9" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2313,12 +2364,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E9" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-after-submit-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_09_instructor_after_submit.png</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
       <x:c r="A10" s="7" t="str">
-        <x:v>instructor-before-buried-directions.png</x:v>
+        <x:v>legacy_s01_canvas_07_instructor_before_buried_directions.png</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2330,12 +2381,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E10" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-buried-directions.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_07_instructor_before_buried_directions.png</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
       <x:c r="A11" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_06_instructor_before_comparison.png</x:v>
       </x:c>
       <x:c r="B11" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2347,12 +2398,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E11" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-comparison-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_06_instructor_before_comparison.png</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
       <x:c r="A12" s="7" t="str">
-        <x:v>instructor-before-module-mobile-phone.png</x:v>
+        <x:v>legacy_s01_canvas_03_instructor_before_module_phone.png</x:v>
       </x:c>
       <x:c r="B12" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2364,12 +2415,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E12" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module-mobile-phone.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_03_instructor_before_module_phone.png</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="7" t="str">
-        <x:v>instructor-before-module-mobile-wide.png</x:v>
+        <x:v>legacy_s01_canvas_02_instructor_before_module_wide.png</x:v>
       </x:c>
       <x:c r="B13" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2381,12 +2432,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E13" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module-mobile-wide.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_02_instructor_before_module_wide.png</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
       <x:c r="A14" s="7" t="str">
-        <x:v>instructor-before-module.png</x:v>
+        <x:v>legacy_s01_canvas_01_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="B14" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2398,12 +2449,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E14" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_01_instructor_before_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
       <x:c r="A15" s="7" t="str">
-        <x:v>instructor-before-week-4-notes.png</x:v>
+        <x:v>legacy_s01_canvas_05_instructor_before_week4_notes.png</x:v>
       </x:c>
       <x:c r="B15" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2415,12 +2466,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E15" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/instructor-before-week-4-notes.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_05_instructor_before_week4_notes.png</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
       <x:c r="A16" s="7" t="str">
-        <x:v>instructor-after-module-focus.png</x:v>
+        <x:v>legacy_s01_board_18_instructor_after_module.png</x:v>
       </x:c>
       <x:c r="B16" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2432,12 +2483,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E16" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_18_instructor_after_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
       <x:c r="A17" s="7" t="str">
-        <x:v>instructor-after-start-here-focus.png</x:v>
+        <x:v>legacy_s01_board_24_instructor_after_start_here.png</x:v>
       </x:c>
       <x:c r="B17" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2449,12 +2500,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E17" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-start-here-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_24_instructor_after_start_here.png</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
       <x:c r="A18" s="7" t="str">
-        <x:v>instructor-after-submit-assignment-focus.png</x:v>
+        <x:v>legacy_s01_board_22_instructor_after_submit.png</x:v>
       </x:c>
       <x:c r="B18" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2466,12 +2517,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E18" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-after-submit-assignment-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_22_instructor_after_submit.png</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
       <x:c r="A19" s="7" t="str">
-        <x:v>instructor-before-buried-directions-focus.png</x:v>
+        <x:v>legacy_s01_board_23_instructor_before_buried.png</x:v>
       </x:c>
       <x:c r="B19" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2483,12 +2534,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E19" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-buried-directions-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_23_instructor_before_buried.png</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
       <x:c r="A20" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment-focus.png</x:v>
+        <x:v>legacy_s01_board_25_instructor_before_comparison_reference.png</x:v>
       </x:c>
       <x:c r="B20" s="7" t="str">
         <x:v>Reference</x:v>
@@ -2500,12 +2551,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E20" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-comparison-assignment-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_25_instructor_before_comparison_reference.png</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
       <x:c r="A21" s="7" t="str">
-        <x:v>instructor-before-comparison-assignment-safe-focus.png</x:v>
+        <x:v>legacy_s01_board_21_instructor_before_comparison_safe.png</x:v>
       </x:c>
       <x:c r="B21" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2517,12 +2568,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E21" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-comparison-assignment-safe-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_21_instructor_before_comparison_safe.png</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
       <x:c r="A22" s="7" t="str">
-        <x:v>instructor-before-module-focus.png</x:v>
+        <x:v>legacy_s01_board_17_instructor_before_module.png</x:v>
       </x:c>
       <x:c r="B22" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2534,12 +2585,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E22" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/instructor-before-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_17_instructor_before_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
       <x:c r="A23" s="7" t="str">
-        <x:v>student-after-module-focus.png</x:v>
+        <x:v>legacy_s01_board_20_student_after_module.png</x:v>
       </x:c>
       <x:c r="B23" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2551,12 +2602,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E23" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/student-after-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_20_student_after_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
       <x:c r="A24" s="7" t="str">
-        <x:v>student-before-module-focus.png</x:v>
+        <x:v>legacy_s01_board_19_student_before_module.png</x:v>
       </x:c>
       <x:c r="B24" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2568,12 +2619,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E24" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/student-before-module-focus.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/smartboard/legacy_s01_board_19_student_before_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
       <x:c r="A25" s="7" t="str">
-        <x:v>student-after-module.png</x:v>
+        <x:v>legacy_s01_canvas_14_student_after_module.png</x:v>
       </x:c>
       <x:c r="B25" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2585,12 +2636,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E25" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-after-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_14_student_after_module.png</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
       <x:c r="A26" s="7" t="str">
-        <x:v>student-after-start-here.png</x:v>
+        <x:v>legacy_s01_canvas_16_student_after_start_here.png</x:v>
       </x:c>
       <x:c r="B26" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2602,12 +2653,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E26" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-after-start-here.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_16_student_after_start_here.png</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
       <x:c r="A27" s="7" t="str">
-        <x:v>student-before-comparison-assignment.png</x:v>
+        <x:v>legacy_s01_canvas_15_student_before_comparison.png</x:v>
       </x:c>
       <x:c r="B27" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2619,12 +2670,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E27" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-comparison-assignment.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_15_student_before_comparison.png</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
       <x:c r="A28" s="7" t="str">
-        <x:v>student-before-module-mobile-phone.png</x:v>
+        <x:v>legacy_s01_canvas_13_student_before_module_phone.png</x:v>
       </x:c>
       <x:c r="B28" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2636,12 +2687,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E28" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module-mobile-phone.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_13_student_before_module_phone.png</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
       <x:c r="A29" s="7" t="str">
-        <x:v>student-before-module-mobile-wide.png</x:v>
+        <x:v>legacy_s01_canvas_12_student_before_module_wide.png</x:v>
       </x:c>
       <x:c r="B29" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2653,12 +2704,12 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E29" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module-mobile-wide.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_12_student_before_module_wide.png</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
       <x:c r="A30" s="7" t="str">
-        <x:v>student-before-module.png</x:v>
+        <x:v>legacy_s01_canvas_11_student_before_module.png</x:v>
       </x:c>
       <x:c r="B30" s="7" t="str">
         <x:v>Runtime</x:v>
@@ -2670,13 +2721,13 @@
         <x:v>Review dormant code and tests</x:v>
       </x:c>
       <x:c r="E30" s="7" t="str">
-        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/student-before-module.png</x:v>
+        <x:v>assets/images/scenes/scenario-01-content-avalanche/canvas/legacy_s01_canvas_11_student_before_module.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3fedb3915764dec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44038b42ab8c407e"/>
   </x:tableParts>
 </x:worksheet>
 </file>